--- a/backtest_runs/20260410_193731/by_symbol/DBCI/DBCI.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DBCI/DBCI.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-6078.479999999992</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>93921.52</v>
@@ -633,7 +633,7 @@
         <v>-17843.28</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>91568.56000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>91568.56000000001</v>
@@ -771,7 +771,7 @@
         <v>-1568.640000000001</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>89999.92000000001</v>
@@ -863,7 +863,7 @@
         <v>-3529.439999999995</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>89607.76000000001</v>
@@ -955,7 +955,7 @@
         <v>-784.3200000000007</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>91176.40000000001</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>91176.40000000001</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>91176.40000000001</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>99803.92000000003</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>99803.92000000003</v>
@@ -1323,7 +1323,7 @@
         <v>-2745.119999999994</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>97058.80000000003</v>
@@ -1415,7 +1415,7 @@
         <v>-3725.520000000008</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>100392.16</v>
@@ -1461,7 +1461,7 @@
         <v>-1764.719999999997</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>98627.44000000003</v>
@@ -1645,7 +1645,7 @@
         <v>-6470.640000000001</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>93333.28000000003</v>
